--- a/form/Routing Form 2026-10-27 (edited).xlsx
+++ b/form/Routing Form 2026-10-27 (edited).xlsx
@@ -107,7 +107,7 @@
     <t>UHC</t>
   </si>
   <si>
-    <t>Other______________</t>
+    <t>Other</t>
   </si>
   <si>
     <t xml:space="preserve">OON __________</t>
